--- a/src/main/resources/excel/Questions.xlsx
+++ b/src/main/resources/excel/Questions.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="951">
   <si>
     <t xml:space="preserve">What</t>
   </si>
@@ -208,7 +208,7 @@
     <t xml:space="preserve">wʌts ðæt nɔɪz ˈaʊtˈsaɪd fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">supplies</t>
+    <t xml:space="preserve">Why did you buy all these supplies? What for?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Por qué compraste todos estos suministros? ¿Para qué?</t>
@@ -217,7 +217,7 @@
     <t xml:space="preserve">waɪ dɪd ju baɪ ɔl ðiz səˈplaɪz? wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">Why did you buy all these supplies? What for?</t>
+    <t xml:space="preserve">I need to borrow your laptop. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Necesito pedir prestado tu portátil. ¿Para qué?</t>
@@ -226,7 +226,7 @@
     <t xml:space="preserve">aɪ nid tu ˈbɑˌroʊ jʊər ˈlæpˌtɑp. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">I need to borrow your laptop. What for?</t>
+    <t xml:space="preserve">She asked me to pick up groceries. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Ella me pidió que comprara alimentos. ¿Para qué?</t>
@@ -235,10 +235,7 @@
     <t xml:space="preserve">ʃi æskt mi tu pɪk ʌp ˈɡroʊsəriz. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">groceries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">She asked me to pick up groceries. What for?</t>
+    <t xml:space="preserve">What's the rush? What for?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Cuál es la prisa? ¿Para qué?</t>
@@ -247,7 +244,7 @@
     <t xml:space="preserve">wʌts ðə rʌʃ? wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">What's the rush? What for?</t>
+    <t xml:space="preserve">I have a doctor's appointment today. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Tengo una cita con el médico hoy. ¿Para qué?</t>
@@ -256,10 +253,7 @@
     <t xml:space="preserve">aɪ hæv ə ˈdɑktərz əˈpɔɪntmənt təˈdeɪ. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">doctor's appointment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I have a doctor's appointment today. What for?</t>
+    <t xml:space="preserve">They're having a meeting later. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Van a tener una reunión más tarde. ¿Para qué?</t>
@@ -268,7 +262,7 @@
     <t xml:space="preserve">ðɛr ˈhævɪŋ ə ˈmitɪŋ ˈleɪtər. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">They're having a meeting later. What for?</t>
+    <t xml:space="preserve">What's all this preparation for?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Para qué es toda esta preparación?</t>
@@ -277,7 +271,7 @@
     <t xml:space="preserve">wʌts ɔl ðɪs ˌprɛpəˈreɪʃən fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">What's all this preparation for?</t>
+    <t xml:space="preserve">He called you urgently. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Te llamó urgentemente. ¿Para qué?</t>
@@ -286,10 +280,7 @@
     <t xml:space="preserve">hi kɔld ju ˈɜrʤəntli. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">urgently</t>
-  </si>
-  <si>
-    <t xml:space="preserve">He called you urgently. What for?</t>
+    <t xml:space="preserve">I'm cleaning the house. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Estoy limpiando la casa. ¿Para qué?</t>
@@ -298,7 +289,7 @@
     <t xml:space="preserve">aɪm ˈklinɪŋ ðə haʊs. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">I'm cleaning the house. What for?</t>
+    <t xml:space="preserve">I need to buy a new car. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Necesito comprar un coche nuevo. ¿Para qué?</t>
@@ -307,16 +298,16 @@
     <t xml:space="preserve">aɪ nid tu baɪ ə nu kɑr. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">I need to buy a new car. What for?</t>
+    <t xml:space="preserve">They invited us to dinner. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Nos invitaron a cenar. ¿Para qué?</t>
   </si>
   <si>
-    <t xml:space="preserve">ðeɪ ɪnˈvaɪtəd ʌs tu ˈdɪnər. wɑt fɔr?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They invited us to dinner. What for?</t>
+    <t xml:space="preserve">ðeɪ ɪnˈvaɪtɪd ʌs tu ˈdɪnər. wɑt fɔr?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I saw you with those tools. What for?</t>
   </si>
   <si>
     <t xml:space="preserve">Te vi con esas herramientas. ¿Para qué?</t>
@@ -325,160 +316,151 @@
     <t xml:space="preserve">aɪ sɔ ju wɪð ðoʊz tulz. wɑt fɔr?</t>
   </si>
   <si>
-    <t xml:space="preserve">I saw you with those tools. What for?</t>
+    <t xml:space="preserve">To Whom</t>
   </si>
   <si>
     <t xml:space="preserve">A quien</t>
   </si>
   <si>
-    <t xml:space="preserve">ə kwiéɛn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To Whom</t>
+    <t xml:space="preserve">tu hum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom did you give the keys?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién le diste las llaves?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn lə diste lɑs llaves?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom did you give the keys?</t>
+    <t xml:space="preserve">tu hum dɪd ju ɡɪv ðə kiz?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom should I address this letter?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién debería dirigir esta carta?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn ˈdiboʊ dirigir ˈɛstə ˈkɑrtə?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom should I address this letter?</t>
+    <t xml:space="preserve">tu hum ʃʊd aɪ ˈæˌdrɛs ðɪs ˈlɛtər?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I need to talk to someone, To whom should I speak?</t>
   </si>
   <si>
     <t xml:space="preserve">Necesito hablar con alguien, ¿Con quién debería hablar?</t>
   </si>
   <si>
-    <t xml:space="preserve">Necesito hablar kɑn alguien ¿kɑn kwiéɛn ˈdiboʊ hablar?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I need to talk to someone, To whom should I speak?</t>
+    <t xml:space="preserve">aɪ nid tu tɔk tu ˈsʌmˌwʌn, tu hum ʃʊd aɪ spik?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He mentioned a friend to whom he owes money</t>
   </si>
   <si>
     <t xml:space="preserve">Mencionó a un amigo a quien debe dinero</t>
   </si>
   <si>
-    <t xml:space="preserve">Mencionó ə ʌn əˈmiˌɡoʊ æl kju lə debe dinero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">He mentioned a friend to whom he owes money</t>
+    <t xml:space="preserve">hi ˈmɛnʃənd ə frɛnd tu hum hi oʊz ˈmʌni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom are you referring in your presentation?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién te estás refiriendo en tu presentación?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn ti ˌriˈfɪrz ɛn tu presentacióɛn?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">referring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom are you referring in your presentation?</t>
+    <t xml:space="preserve">tu hum ɑr ju rɪˈfɜrɪŋ ɪn jʊər ˌprɛzənˈteɪʃən?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I sent an email to whom it may concern</t>
   </si>
   <si>
     <t xml:space="preserve">Envié un correo electrónico a quien corresponda</t>
   </si>
   <si>
-    <t xml:space="preserve">Envié ʌn correo electróˈnikoʊ ə quien pueda interesar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I sent an email to whom it may concern</t>
+    <t xml:space="preserve">aɪ sɛnt ən iˈmeɪl tu hum ɪt meɪ kənˈsɜrn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom did they give the award?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién le dieron el premio?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn lə dieron ɛl premio?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">award</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom did they give the award?</t>
+    <t xml:space="preserve">tu hum dɪd ðeɪ ɡɪv ði əˈwɔrd?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom should I report this incident?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién debería informar sobre este incidente?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn ˈdiboʊ reportar ɛst incidente?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom should I report this incident?</t>
+    <t xml:space="preserve">tu hum ʃʊd aɪ rɪˈpɔrt ðɪs ˈɪnsədənt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He handed the document to whom he believed was in charge</t>
   </si>
   <si>
     <t xml:space="preserve">Entregó el documento a quien creía que estaba a cargo</t>
   </si>
   <si>
-    <t xml:space="preserve">lə entregó ɛl documento ə quien creíə kju estaba ə ˈkɑrˌɡoʊ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">He handed the document to whom he believed was in charge</t>
+    <t xml:space="preserve">hi ˈhændɪd ðə ˈdɑkjəmɛnt tu hum hi bɪˈlivd wʌz ɪn ʧɑrʤ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom do you owe a debt of gratitude?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién le debes una deuda de gratitud?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿kɑn kwiéɛn tjɛnz ˈunə deuda di gratitud?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom do you owe a debt of gratitude?</t>
+    <t xml:space="preserve">tu hum du ju oʊ ə dɛt ʌv ˈɡrætəˌtud?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'll introduce you to the person to whom you'll be reporting</t>
   </si>
   <si>
     <t xml:space="preserve">Te presentaré a la persona a quien informarás</t>
   </si>
   <si>
-    <t xml:space="preserve">ti presentaré ə lɑ pərˈsoʊnə ə quien reportaráɛs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I'll introduce you to the person to whom you'll be reporting</t>
+    <t xml:space="preserve">aɪl ˌɪntrəˈdus ju tu ðə ˈpɜrsən tu hum jul bi rɪˈpɔrtɪŋ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom did she entrust her secrets?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién le confió sus secretos?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn confió sʌs secretos?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom did she entrust her secrets?</t>
+    <t xml:space="preserve">tu hum dɪd ʃi ɛnˈtrʌst hɜr ˈsikrəts?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We need to find out to whom this belongs</t>
   </si>
   <si>
     <t xml:space="preserve">Necesitamos descubrir a quién pertenece esto</t>
   </si>
   <si>
-    <t xml:space="preserve">Necesitamos ˈseɪbər ə kwiéɛn pertenece esto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We need to find out to whom this belongs</t>
+    <t xml:space="preserve">wi nid tu faɪnd aʊt tu hum ðɪs bɪˈlɔŋz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'll talk to the professor to whom you referred me</t>
   </si>
   <si>
     <t xml:space="preserve">Hablaré con el profesor al que me referiste</t>
   </si>
   <si>
-    <t xml:space="preserve">Hablaré kɑn ɛl profesor æl kju mi recomendaste.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I'll talk to the professor to whom you referred me</t>
+    <t xml:space="preserve">aɪl tɔk tu ðə prəˈfɛsər tu hum ju rəˈfɜrd mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To whom did you lend your camera?</t>
   </si>
   <si>
     <t xml:space="preserve">¿A quién prestaste tu cámara?</t>
   </si>
   <si>
-    <t xml:space="preserve">¿ə kwiéɛn lə prestaste tu siáˈmɑrə?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To whom did you lend your camera?</t>
+    <t xml:space="preserve">tu hum dɪd ju lɛnd jʊər ˈkæmərə?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whom</t>
   </si>
   <si>
     <t xml:space="preserve">Con Quien</t>
@@ -487,7 +469,7 @@
     <t xml:space="preserve">hum</t>
   </si>
   <si>
-    <t xml:space="preserve">Whom</t>
+    <t xml:space="preserve">Whom did you go to the party with?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Con quién fuiste a la fiesta?</t>
@@ -496,7 +478,7 @@
     <t xml:space="preserve">hum dɪd ju ɡoʊ tu ðə ˈpɑrti wɪð?</t>
   </si>
   <si>
-    <t xml:space="preserve">Whom did you go to the party with?</t>
+    <t xml:space="preserve">I don't know with whom she went on vacation</t>
   </si>
   <si>
     <t xml:space="preserve">No sé con quién se fue de vacaciones.</t>
@@ -505,7 +487,7 @@
     <t xml:space="preserve">aɪ doʊnt noʊ wɪð hum ʃi wɛnt ɑn veɪˈkeɪʃən</t>
   </si>
   <si>
-    <t xml:space="preserve">I don't know with whom she went on vacation</t>
+    <t xml:space="preserve">He's the person with whom I discussed the project</t>
   </si>
   <si>
     <t xml:space="preserve">Es la persona con la que discutí el proyecto.</t>
@@ -514,7 +496,7 @@
     <t xml:space="preserve">hiz ðə ˈpɜrsən wɪð hum aɪ dɪˈskʌst ðə ˈprɑʤɛkt</t>
   </si>
   <si>
-    <t xml:space="preserve">He's the person with whom I discussed the project</t>
+    <t xml:space="preserve">With whom are you planning to have dinner tonight?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Con quién planeas cenar esta noche?</t>
@@ -523,7 +505,7 @@
     <t xml:space="preserve">wɪð hum ɑr ju ˈplænɪŋ tu hæv ˈdɪnər təˈnaɪt?</t>
   </si>
   <si>
-    <t xml:space="preserve">With whom are you planning to have dinner tonight?</t>
+    <t xml:space="preserve">That's the team with whom we'll be working closely</t>
   </si>
   <si>
     <t xml:space="preserve">Ese es el equipo con el que trabajaremos estrechamente.</t>
@@ -532,7 +514,7 @@
     <t xml:space="preserve">ðæts ðə tim wɪð hum wil bi ˈwɜrkɪŋ ˈkloʊsli</t>
   </si>
   <si>
-    <t xml:space="preserve">That's the team with whom we'll be working closely</t>
+    <t xml:space="preserve">She's the one with whom I had a long conversation</t>
   </si>
   <si>
     <t xml:space="preserve">Ella es la que con quien tuve una larga conversación.</t>
@@ -541,7 +523,7 @@
     <t xml:space="preserve">ʃiz ðə wʌn wɪð hum aɪ hæd ə lɔŋ ˌkɑnvərˈseɪʃən</t>
   </si>
   <si>
-    <t xml:space="preserve">She's the one with whom I had a long conversation</t>
+    <t xml:space="preserve">I found the keys with which I can open the door</t>
   </si>
   <si>
     <t xml:space="preserve">Encontré las llaves con las que puedo abrir la puerta.</t>
@@ -550,7 +532,7 @@
     <t xml:space="preserve">aɪ faʊnd ðə kiz wɪð wɪʧ aɪ kæn ˈoʊpən ðə dɔr</t>
   </si>
   <si>
-    <t xml:space="preserve">I found the keys with which I can open the door</t>
+    <t xml:space="preserve">With whom would you like to go to the movies?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Con quién te gustaría ir al cine?</t>
@@ -559,7 +541,7 @@
     <t xml:space="preserve">wɪð hum wʊd ju laɪk tu ɡoʊ tu ðə ˈmuviz?</t>
   </si>
   <si>
-    <t xml:space="preserve">With whom would you like to go to the movies?</t>
+    <t xml:space="preserve">He's the lawyer with whom I'm discussing my case</t>
   </si>
   <si>
     <t xml:space="preserve">Él es el abogado con el que estoy discutiendo mi caso.</t>
@@ -568,7 +550,7 @@
     <t xml:space="preserve">hiz ðə ˈlɔjər wɪð hum aɪm dɪˈskʌsɪŋ maɪ keɪs</t>
   </si>
   <si>
-    <t xml:space="preserve">He's the lawyer with whom I'm discussing my case</t>
+    <t xml:space="preserve">I can't remember with whom I had lunch yesterday</t>
   </si>
   <si>
     <t xml:space="preserve">No puedo recordar con quién almorcé ayer.</t>
@@ -577,7 +559,7 @@
     <t xml:space="preserve">aɪ kænt rɪˈmɛmbər wɪð hum aɪ hæd lʌnʧ ˈjɛstərˌdeɪ</t>
   </si>
   <si>
-    <t xml:space="preserve">I can't remember with whom I had lunch yesterday</t>
+    <t xml:space="preserve">With whom do you want to share this news first?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Con quién quieres compartir esta noticia primero?</t>
@@ -586,7 +568,7 @@
     <t xml:space="preserve">wɪð hum du ju wɑnt tu ʃɛr ðɪs nuz fɜrst?</t>
   </si>
   <si>
-    <t xml:space="preserve">With whom do you want to share this news first?</t>
+    <t xml:space="preserve">It's the book with which I learned a lot about history</t>
   </si>
   <si>
     <t xml:space="preserve">Es el libro con el que aprendí mucho sobre historia.</t>
@@ -595,7 +577,7 @@
     <t xml:space="preserve">ɪts ðə bʊk wɪð wɪʧ aɪ lɜrnd ə lɑt əˈbaʊt ˈhɪstəri</t>
   </si>
   <si>
-    <t xml:space="preserve">It's the book with which I learned a lot about history</t>
+    <t xml:space="preserve">With whom did you attend the conference last week?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Con quién asististe a la conferencia la semana pasada?</t>
@@ -604,7 +586,7 @@
     <t xml:space="preserve">wɪð hum dɪd ju əˈtɛnd ðə ˈkɑnfərəns læst wik?</t>
   </si>
   <si>
-    <t xml:space="preserve">With whom did you attend the conference last week?</t>
+    <t xml:space="preserve">She's the friend with whom I traveled to Europe</t>
   </si>
   <si>
     <t xml:space="preserve">Ella es la amiga con la que viajé a Europa.</t>
@@ -613,7 +595,7 @@
     <t xml:space="preserve">ʃiz ðə frɛnd wɪð hum aɪ ˈtrævəld tu ˈjʊrəp</t>
   </si>
   <si>
-    <t xml:space="preserve">She's the friend with whom I traveled to Europe</t>
+    <t xml:space="preserve">Whom should I contact with regard to this issue?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Con quién debo contactar con respecto a este problema?</t>
@@ -622,10 +604,7 @@
     <t xml:space="preserve">hum ʃʊd aɪ ˈkɑnˌtækt wɪð rəˈɡɑrd tu ðɪs ˈɪʃu?</t>
   </si>
   <si>
-    <t xml:space="preserve">regard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whom should I contact with regard to this issue?</t>
+    <t xml:space="preserve">From Where</t>
   </si>
   <si>
     <t xml:space="preserve">De donde</t>
@@ -634,7 +613,7 @@
     <t xml:space="preserve">frʌm wɛr</t>
   </si>
   <si>
-    <t xml:space="preserve">from Where</t>
+    <t xml:space="preserve">Where did you come from?</t>
   </si>
   <si>
     <t xml:space="preserve">¿De dónde vienes?</t>
@@ -643,7 +622,7 @@
     <t xml:space="preserve">wɛr dɪd ju kʌm frʌm?</t>
   </si>
   <si>
-    <t xml:space="preserve">Where did you come from?</t>
+    <t xml:space="preserve">From where does this delicious food come?</t>
   </si>
   <si>
     <t xml:space="preserve">¿De dónde proviene esta deliciosa comida?</t>
@@ -652,7 +631,7 @@
     <t xml:space="preserve">frʌm wɛr dʌz ðɪs dɪˈlɪʃəs fud kʌm?</t>
   </si>
   <si>
-    <t xml:space="preserve">From where does this delicious food come?</t>
+    <t xml:space="preserve">I wonder from where she got that idea</t>
   </si>
   <si>
     <t xml:space="preserve">Me pregunto de dónde sacó esa idea</t>
@@ -661,7 +640,7 @@
     <t xml:space="preserve">aɪ ˈwʌndər frʌm wɛr ʃi ɡɑt ðæt aɪˈdiə</t>
   </si>
   <si>
-    <t xml:space="preserve">I wonder from where she got that idea</t>
+    <t xml:space="preserve">Do you know from where the bus departs?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Sabes de dónde parte el autobús?</t>
@@ -670,7 +649,7 @@
     <t xml:space="preserve">du ju noʊ frʌm wɛr ðə bʌs dɪˈpɑrts?</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you know from where the bus departs?</t>
+    <t xml:space="preserve">From where I'm sitting, I can see the whole city</t>
   </si>
   <si>
     <t xml:space="preserve">Desde donde estoy sentado, puedo ver toda la ciudad</t>
@@ -679,7 +658,7 @@
     <t xml:space="preserve">frʌm wɛr aɪm ˈsɪtɪŋ, aɪ kæn si ðə hoʊl ˈsɪti</t>
   </si>
   <si>
-    <t xml:space="preserve">From where I'm sitting, I can see the whole city</t>
+    <t xml:space="preserve">He asked me from where I had learned to dance</t>
   </si>
   <si>
     <t xml:space="preserve">Me preguntó de dónde había aprendido a bailar</t>
@@ -688,7 +667,7 @@
     <t xml:space="preserve">hi æskt mi frʌm wɛr aɪ hæd lɜrnd tu dæns</t>
   </si>
   <si>
-    <t xml:space="preserve">He asked me from where I had learned to dance</t>
+    <t xml:space="preserve">Can you tell me from where this music is coming?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Puedes decirme de dónde viene esta música?</t>
@@ -697,7 +676,7 @@
     <t xml:space="preserve">kæn ju tɛl mi frʌm wɛr ðɪs ˈmjuzɪk ɪz ˈkʌmɪŋ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Can you tell me from where this music is coming?</t>
+    <t xml:space="preserve">From where I stand, everything looks beautiful</t>
   </si>
   <si>
     <t xml:space="preserve">Desde donde estoy parado, todo se ve hermoso</t>
@@ -706,7 +685,7 @@
     <t xml:space="preserve">frʌm wɛr aɪ stænd, ˈɛvriˌθɪŋ lʊks ˈbjutəfəl</t>
   </si>
   <si>
-    <t xml:space="preserve">From where I stand, everything looks beautiful</t>
+    <t xml:space="preserve">I can't remember from where I heard that song before</t>
   </si>
   <si>
     <t xml:space="preserve">No puedo recordar de dónde escuché esa canción antes</t>
@@ -715,7 +694,7 @@
     <t xml:space="preserve">aɪ kænt rɪˈmɛmbər frʌm wɛr aɪ hɜrd ðæt sɔŋ bɪˈfɔr</t>
   </si>
   <si>
-    <t xml:space="preserve">I can't remember from where I heard that song before</t>
+    <t xml:space="preserve">From where I'm coming, the traffic is terrible</t>
   </si>
   <si>
     <t xml:space="preserve">Desde donde vengo, el tráfico es terrible</t>
@@ -724,7 +703,7 @@
     <t xml:space="preserve">frʌm wɛr aɪm ˈkʌmɪŋ, ðə ˈtræfɪk ɪz ˈtɛrəbəl</t>
   </si>
   <si>
-    <t xml:space="preserve">From where I'm coming, the traffic is terrible</t>
+    <t xml:space="preserve">Do you know from where the rumors are spreading?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Sabes de dónde se están propagando los rumores?</t>
@@ -733,7 +712,7 @@
     <t xml:space="preserve">du ju noʊ frʌm wɛr ðə ˈrumərz ɑr ˈsprɛdɪŋ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you know from where the rumors are spreading?</t>
+    <t xml:space="preserve">I can't tell from where that sound is coming</t>
   </si>
   <si>
     <t xml:space="preserve">No puedo decir de dónde viene ese sonido</t>
@@ -742,7 +721,7 @@
     <t xml:space="preserve">aɪ kænt tɛl frʌm wɛr ðæt saʊnd ɪz ˈkʌmɪŋ</t>
   </si>
   <si>
-    <t xml:space="preserve">I can't tell from where that sound is coming</t>
+    <t xml:space="preserve">From where I'm standing, I can't see the stage</t>
   </si>
   <si>
     <t xml:space="preserve">Desde donde estoy parado, no puedo ver el escenario</t>
@@ -751,7 +730,7 @@
     <t xml:space="preserve">frʌm wɛr aɪm ˈstændɪŋ, aɪ kænt si ðə steɪʤ</t>
   </si>
   <si>
-    <t xml:space="preserve">From where I'm standing, I can't see the stage</t>
+    <t xml:space="preserve">I asked her from where she had bought those shoes</t>
   </si>
   <si>
     <t xml:space="preserve">Le pregunté de dónde había comprado esos zapatos</t>
@@ -760,7 +739,7 @@
     <t xml:space="preserve">aɪ æskt hɜr frʌm wɛr ʃi hæd bɑt ðoʊz ʃuz</t>
   </si>
   <si>
-    <t xml:space="preserve">I asked her from where she had bought those shoes</t>
+    <t xml:space="preserve">From where you are, can you see the ocean?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Desde donde estás, puedes ver el océano?</t>
@@ -769,7 +748,7 @@
     <t xml:space="preserve">frʌm wɛr ju ɑr, kæn ju si ði ˈoʊʃən?</t>
   </si>
   <si>
-    <t xml:space="preserve">From where you are, can you see the ocean?</t>
+    <t xml:space="preserve">How about</t>
   </si>
   <si>
     <t xml:space="preserve">Que tal</t>
@@ -778,7 +757,7 @@
     <t xml:space="preserve">haʊ əˈbaʊt</t>
   </si>
   <si>
-    <t xml:space="preserve">How about</t>
+    <t xml:space="preserve">How about going to the movies tonight?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué tal si vamos al cine esta noche?</t>
@@ -787,7 +766,7 @@
     <t xml:space="preserve">haʊ əˈbaʊt ˈɡoʊɪŋ tu ðə ˈmuviz təˈnaɪt?</t>
   </si>
   <si>
-    <t xml:space="preserve">How about going to the movies tonight?</t>
+    <t xml:space="preserve">How 'bout we grab a coffee after work?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece si tomamos un café después del trabajo?</t>
@@ -796,7 +775,7 @@
     <t xml:space="preserve">haʊ baʊt wi ɡræb ə ˈkɑfi ˈæftər wɜrk?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout we grab a coffee after work?</t>
+    <t xml:space="preserve">How 'bout we meet at 2 o'clock?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué tal si nos encontramos a las 2 en punto?</t>
@@ -805,7 +784,7 @@
     <t xml:space="preserve">haʊ baʊt wi mit æt 2 əˈklɑk?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout we meet at 2 o'clock?</t>
+    <t xml:space="preserve">How 'bout going for a walk in the park?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece si damos un paseo por el parque?</t>
@@ -814,7 +793,7 @@
     <t xml:space="preserve">haʊ baʊt ˈɡoʊɪŋ fɔr ə wɔk ɪn ðə pɑrk?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout going for a walk in the park?</t>
+    <t xml:space="preserve">How 'bout some pizza for dinner?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece una pizza para cenar?</t>
@@ -823,7 +802,7 @@
     <t xml:space="preserve">haʊ baʊt sʌm ˈpitsə fɔr ˈdɪnər?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout some pizza for dinner?</t>
+    <t xml:space="preserve">How about taking a day off next week?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué tal si tomamos un día libre la próxima semana?</t>
@@ -832,7 +811,7 @@
     <t xml:space="preserve">haʊ əˈbaʊt ˈteɪkɪŋ ə deɪ ɔf nɛkst wik?</t>
   </si>
   <si>
-    <t xml:space="preserve">How about taking a day off next week?</t>
+    <t xml:space="preserve">How 'bout we skip the gym today?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece si nos saltamos el gimnasio hoy?</t>
@@ -841,7 +820,7 @@
     <t xml:space="preserve">haʊ baʊt wi skɪp ðə ʤɪm təˈdeɪ?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout we skip the gym today?</t>
+    <t xml:space="preserve">How 'bout going shopping this weekend?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece ir de compras este fin de semana?</t>
@@ -850,7 +829,7 @@
     <t xml:space="preserve">haʊ baʊt ˈɡoʊɪŋ ˈʃɑpɪŋ ðɪs ˈwiˌkɛnd?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout going shopping this weekend?</t>
+    <t xml:space="preserve">How 'bout we try that new restaurant downtown?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece si probamos ese restaurante nuevo en el centro?</t>
@@ -859,7 +838,7 @@
     <t xml:space="preserve">haʊ baʊt wi traɪ ðæt nu ˈrɛstəˌrɑnt ˈdaʊnˈtaʊn?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout we try that new restaurant downtown?</t>
+    <t xml:space="preserve">How 'bout a game of chess?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece una partida de ajedrez?</t>
@@ -868,10 +847,7 @@
     <t xml:space="preserve">haʊ baʊt ə ɡeɪm ʌv ʧɛs?</t>
   </si>
   <si>
-    <t xml:space="preserve">chess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How 'bout a game of chess?</t>
+    <t xml:space="preserve">How 'bout we visit your parents on Sunday?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué tal si visitamos a tus padres el domingo?</t>
@@ -880,7 +856,7 @@
     <t xml:space="preserve">haʊ baʊt wi ˈvɪzət jʊər ˈpɛrənts ɑn ˈsʌnˌdeɪ?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout we visit your parents on Sunday?</t>
+    <t xml:space="preserve">How 'bout catching a matinee show on Saturday?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece si vamos a ver una película en la sesión de la tarde del sábado?</t>
@@ -889,10 +865,7 @@
     <t xml:space="preserve">haʊ baʊt ˈkæʧɪŋ ə ˈmætɪˌneɪ ʃoʊ ɑn ˈsætərˌdeɪ?</t>
   </si>
   <si>
-    <t xml:space="preserve">matinee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How 'bout catching a matinee show on Saturday?</t>
+    <t xml:space="preserve">How 'bout inviting Sarah to the party?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece invitar a Sarah a la fiesta?</t>
@@ -901,7 +874,7 @@
     <t xml:space="preserve">haʊ baʊt ɪnˈvaɪtɪŋ ˈsɛrə tu ðə ˈpɑrti?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout inviting Sarah to the party?</t>
+    <t xml:space="preserve">How 'bout going for a swim in the afternoon?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué te parece si vamos a nadar por la tarde?</t>
@@ -910,7 +883,7 @@
     <t xml:space="preserve">haʊ baʊt ˈɡoʊɪŋ fɔr ə swɪm ɪn ði ˌæftərˈnun?</t>
   </si>
   <si>
-    <t xml:space="preserve">How 'bout going for a swim in the afternoon?</t>
+    <t xml:space="preserve">How about trying that new dessert at the bakery?</t>
   </si>
   <si>
     <t xml:space="preserve">¿Qué tal si probamos ese postre nuevo en la panadería?</t>
@@ -919,12 +892,6 @@
     <t xml:space="preserve">haʊ əˈbaʊt ˈtraɪɪŋ ðæt nu dɪˈzɜrt æt ðə ˈbeɪkəri?</t>
   </si>
   <si>
-    <t xml:space="preserve">dessert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How about trying that new dessert at the bakery?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Who</t>
   </si>
   <si>
@@ -1783,9 +1750,6 @@
     <t xml:space="preserve">to whom</t>
   </si>
   <si>
-    <t xml:space="preserve">tu hum</t>
-  </si>
-  <si>
     <t xml:space="preserve">Whom did you invite to the party?</t>
   </si>
   <si>
@@ -1814,9 +1778,6 @@
   </si>
   <si>
     <t xml:space="preserve">¿A quién debo dirigir esta carta?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tu hum ʃʊd aɪ ˈæˌdrɛs ðɪs ˈlɛtər?</t>
   </si>
   <si>
     <t xml:space="preserve">Whom did they blame for the mistake?</t>
@@ -3002,7 +2963,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3020,6 +2981,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3150,10 +3115,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="85.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="53.6"/>
@@ -3451,6 +3416,7 @@
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -3484,17 +3450,25 @@
       <c r="A24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
@@ -3502,33 +3476,39 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
@@ -3536,13 +3516,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
@@ -3550,33 +3530,39 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F31" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
@@ -3584,13 +3570,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
@@ -3598,13 +3584,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
@@ -3612,39 +3598,39 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
@@ -3652,13 +3638,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>6</v>
@@ -3666,13 +3652,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
@@ -3680,13 +3666,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
@@ -3694,33 +3680,39 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
@@ -3728,33 +3720,39 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="F44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
@@ -3762,13 +3760,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
@@ -3776,13 +3774,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>6</v>
@@ -3790,13 +3788,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
@@ -3804,33 +3802,39 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
@@ -3838,13 +3842,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
@@ -3852,39 +3856,39 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F55" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
@@ -3892,13 +3896,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>6</v>
@@ -3906,13 +3910,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
@@ -3920,13 +3924,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
@@ -3934,13 +3938,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>6</v>
@@ -3948,13 +3952,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
@@ -3962,13 +3966,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>6</v>
@@ -3976,13 +3980,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>6</v>
@@ -3990,13 +3994,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>6</v>
@@ -4004,13 +4008,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>6</v>
@@ -4018,13 +4022,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>6</v>
@@ -4032,13 +4036,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
@@ -4046,13 +4050,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>6</v>
@@ -4060,13 +4064,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
@@ -4074,45 +4078,51 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="F71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F72" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
@@ -4120,13 +4130,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>6</v>
@@ -4134,13 +4144,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>6</v>
@@ -4148,13 +4158,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>6</v>
@@ -4162,13 +4172,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>6</v>
@@ -4176,13 +4186,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>6</v>
@@ -4190,13 +4200,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
@@ -4204,13 +4214,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>6</v>
@@ -4218,13 +4228,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>6</v>
@@ -4232,13 +4242,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>6</v>
@@ -4246,13 +4256,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>6</v>
@@ -4260,13 +4270,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>6</v>
@@ -4274,13 +4284,13 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
@@ -4288,13 +4298,13 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>6</v>
@@ -4302,39 +4312,39 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F88" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>6</v>
@@ -4342,13 +4352,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>6</v>
@@ -4356,13 +4366,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>6</v>
@@ -4370,13 +4380,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>6</v>
@@ -4384,13 +4394,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>6</v>
@@ -4398,13 +4408,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>6</v>
@@ -4412,13 +4422,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>6</v>
@@ -4426,137 +4436,16 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="F99" s="2"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F102" s="2"/>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="F106" s="2"/>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4587,25 +4476,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -4613,13 +4502,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>6</v>
@@ -4627,13 +4516,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
@@ -4641,13 +4530,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
@@ -4655,13 +4544,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>6</v>
@@ -4669,13 +4558,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>6</v>
@@ -4683,13 +4572,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>6</v>
@@ -4697,13 +4586,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
@@ -4711,13 +4600,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
@@ -4725,13 +4614,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
@@ -4739,13 +4628,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>6</v>
@@ -4753,13 +4642,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
@@ -4767,13 +4656,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
@@ -4781,13 +4670,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
@@ -4795,25 +4684,25 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
@@ -4821,13 +4710,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
@@ -4835,13 +4724,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -4849,13 +4738,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
@@ -4863,13 +4752,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
@@ -4877,13 +4766,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
@@ -4891,13 +4780,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
@@ -4905,13 +4794,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>6</v>
@@ -4919,13 +4808,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
@@ -4933,13 +4822,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
@@ -4947,13 +4836,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
@@ -4961,13 +4850,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
@@ -4975,13 +4864,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
@@ -4989,13 +4878,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
@@ -5003,13 +4892,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
@@ -5017,25 +4906,25 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
@@ -5043,13 +4932,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
@@ -5057,13 +4946,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
@@ -5071,13 +4960,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
@@ -5085,13 +4974,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
@@ -5099,13 +4988,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>6</v>
@@ -5113,13 +5002,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
@@ -5127,13 +5016,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
@@ -5141,13 +5030,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
@@ -5155,13 +5044,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>6</v>
@@ -5169,13 +5058,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
@@ -5183,13 +5072,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>6</v>
@@ -5197,13 +5086,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>6</v>
@@ -5211,13 +5100,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
@@ -5225,13 +5114,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
@@ -5239,221 +5128,221 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
+      <c r="D52" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="F52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="D53" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="F53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
+      <c r="D54" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
+      <c r="D55" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
+      <c r="D56" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
+      <c r="D57" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
+      <c r="D58" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="D59" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="D60" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="D61" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="D62" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+      <c r="D63" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>6</v>
@@ -5461,25 +5350,25 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="F64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>6</v>
@@ -5487,13 +5376,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>6</v>
@@ -5501,13 +5390,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
@@ -5515,13 +5404,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>6</v>
@@ -5529,13 +5418,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
@@ -5543,13 +5432,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>6</v>
@@ -5557,13 +5446,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>6</v>
@@ -5571,13 +5460,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>6</v>
@@ -5585,13 +5474,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
@@ -5599,13 +5488,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>6</v>
@@ -5613,13 +5502,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>6</v>
@@ -5627,13 +5516,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>6</v>
@@ -5641,13 +5530,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>6</v>
@@ -5655,13 +5544,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>6</v>
@@ -5669,13 +5558,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
@@ -5683,25 +5572,25 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="F80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>6</v>
@@ -5709,13 +5598,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>6</v>
@@ -5723,13 +5612,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>6</v>
@@ -5737,13 +5626,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>6</v>
@@ -5751,13 +5640,13 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
@@ -5765,27 +5654,27 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="s">
-        <v>558</v>
+      <c r="A87" s="6" t="s">
+        <v>547</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>6</v>
@@ -5793,111 +5682,111 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="F91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="s">
+      <c r="D92" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="F92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="s">
+      <c r="D93" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="F93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="s">
+      <c r="D94" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="F94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
+      <c r="D95" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>6</v>
@@ -5931,25 +5820,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>586</v>
+        <v>99</v>
       </c>
       <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -5957,13 +5846,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>6</v>
@@ -5971,13 +5860,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
@@ -5985,13 +5874,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>597</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
@@ -5999,13 +5888,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>6</v>
@@ -6013,13 +5902,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>6</v>
@@ -6027,13 +5916,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>6</v>
@@ -6041,13 +5930,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
@@ -6055,13 +5944,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
@@ -6069,13 +5958,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
@@ -6083,13 +5972,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>6</v>
@@ -6097,13 +5986,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
@@ -6111,13 +6000,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
@@ -6125,13 +6014,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
@@ -6139,13 +6028,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
@@ -6153,25 +6042,25 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
@@ -6179,13 +6068,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -6193,13 +6082,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
@@ -6207,13 +6096,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
@@ -6221,13 +6110,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
@@ -6235,13 +6124,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
@@ -6249,13 +6138,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>6</v>
@@ -6263,13 +6152,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
@@ -6277,13 +6166,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
@@ -6291,13 +6180,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
@@ -6305,13 +6194,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
@@ -6319,13 +6208,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
@@ -6333,13 +6222,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
@@ -6347,13 +6236,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
@@ -6361,13 +6250,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
@@ -6375,25 +6264,25 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
@@ -6401,13 +6290,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
@@ -6415,13 +6304,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
@@ -6429,13 +6318,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
@@ -6443,13 +6332,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>6</v>
@@ -6457,13 +6346,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
@@ -6471,13 +6360,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
@@ -6485,13 +6374,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
@@ -6499,13 +6388,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>6</v>
@@ -6513,13 +6402,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
@@ -6527,13 +6416,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>6</v>
@@ -6541,13 +6430,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>6</v>
@@ -6555,13 +6444,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
@@ -6569,13 +6458,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
@@ -6583,13 +6472,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>6</v>
@@ -6597,25 +6486,25 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>6</v>
@@ -6623,13 +6512,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>6</v>
@@ -6637,13 +6526,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
@@ -6651,13 +6540,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
@@ -6665,13 +6554,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
@@ -6679,13 +6568,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
@@ -6693,13 +6582,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
@@ -6707,13 +6596,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>6</v>
@@ -6721,13 +6610,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
@@ -6735,13 +6624,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
@@ -6749,13 +6638,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>6</v>
@@ -6763,13 +6652,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
@@ -6777,13 +6666,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>6</v>
@@ -6791,13 +6680,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>6</v>
@@ -6805,13 +6694,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>6</v>
@@ -6844,222 +6733,222 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>778</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>783</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>787</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>790</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D11" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="F12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>808</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="D16" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>820</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>822</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
@@ -7067,13 +6956,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
@@ -7081,13 +6970,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
@@ -7095,13 +6984,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -7109,13 +6998,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
@@ -7123,13 +7012,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
@@ -7137,13 +7026,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
@@ -7151,13 +7040,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
@@ -7165,13 +7054,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>6</v>
@@ -7179,13 +7068,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
@@ -7193,13 +7082,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
@@ -7207,13 +7096,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
@@ -7221,13 +7110,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
@@ -7235,13 +7124,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
@@ -7249,13 +7138,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
@@ -7263,13 +7152,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
@@ -7277,13 +7166,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
@@ -7291,13 +7180,13 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
@@ -7305,13 +7194,13 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
@@ -7319,13 +7208,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
@@ -7333,13 +7222,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
@@ -7347,13 +7236,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
@@ -7361,13 +7250,13 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>6</v>
@@ -7375,13 +7264,13 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
@@ -7389,13 +7278,13 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
@@ -7403,13 +7292,13 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
@@ -7417,13 +7306,13 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>6</v>
@@ -7431,13 +7320,13 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
@@ -7445,13 +7334,13 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>6</v>
@@ -7459,13 +7348,13 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>6</v>
@@ -7473,13 +7362,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
@@ -7487,13 +7376,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
@@ -7501,13 +7390,13 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>6</v>
@@ -7515,13 +7404,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
@@ -7529,13 +7418,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>6</v>
@@ -7543,13 +7432,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>6</v>
@@ -7557,13 +7446,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
@@ -7571,13 +7460,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
@@ -7585,13 +7474,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
@@ -7599,13 +7488,13 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
@@ -7613,13 +7502,13 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
@@ -7627,13 +7516,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>6</v>
@@ -7641,13 +7530,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
@@ -7655,13 +7544,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
@@ -7669,13 +7558,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>6</v>
@@ -7683,13 +7572,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
@@ -7697,13 +7586,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>6</v>
@@ -7711,13 +7600,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>6</v>
